--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95E92ECA-6BA9-46A6-ACB9-7C651F6703C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36F30891-CD39-433E-871F-B5267F4DFC10}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{732F988F-79E1-4F6C-B2FF-9886F7533E0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0185F8E2-46C2-4043-975B-0A339263AE0A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEE9A68D-FDEA-48D0-9D2A-8BDB6E2D512C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51828C0E-3277-41FB-AE77-85B096C59302}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -953,22 +953,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36F30891-CD39-433E-871F-B5267F4DFC10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3102256B-0744-4C8B-8582-1441574EA7DD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0185F8E2-46C2-4043-975B-0A339263AE0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9BC9B5-E0B5-4D42-9327-2904A1A8DD5B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51828C0E-3277-41FB-AE77-85B096C59302}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F4A6F64-E05A-47A2-A9CD-9FD94F3DC5FD}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3102256B-0744-4C8B-8582-1441574EA7DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8FAD655-47AA-4484-B85C-C8532B415AC4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9BC9B5-E0B5-4D42-9327-2904A1A8DD5B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5925B58-036A-4B97-8736-AE9154198D76}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F4A6F64-E05A-47A2-A9CD-9FD94F3DC5FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC41E9AA-DCD6-46A6-B584-DB00F3FFF348}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -953,22 +953,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36F30891-CD39-433E-871F-B5267F4DFC10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13D724C7-0D25-4703-B00B-982B63C2BBA6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0185F8E2-46C2-4043-975B-0A339263AE0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D71B153C-A8A6-4C35-889C-D2FC53FBB6FD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51828C0E-3277-41FB-AE77-85B096C59302}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A416556D-FE10-42A9-B268-A997B00EBC21}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8FAD655-47AA-4484-B85C-C8532B415AC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FA306F8-4909-41B0-82DF-0C08FAA394B3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5925B58-036A-4B97-8736-AE9154198D76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F72775A7-0B9C-4A6B-A435-009C70EB74A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC41E9AA-DCD6-46A6-B584-DB00F3FFF348}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{794653F4-399A-4C5F-995D-EEC0F72DA063}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FA306F8-4909-41B0-82DF-0C08FAA394B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4916F180-B2AD-4F8A-AA4C-7DC849208C39}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F72775A7-0B9C-4A6B-A435-009C70EB74A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98A9B6A2-D203-4473-98E2-75E409091E40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{794653F4-399A-4C5F-995D-EEC0F72DA063}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D44F5270-FF27-47D3-9492-76735BB1F73B}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4916F180-B2AD-4F8A-AA4C-7DC849208C39}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83E2AA11-741A-4372-AF00-AE5941BF3DF5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98A9B6A2-D203-4473-98E2-75E409091E40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{139662B8-254F-4C6E-8F47-0BED968900AC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D44F5270-FF27-47D3-9492-76735BB1F73B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F8719C4-2E8B-4202-B0B6-BDD2BA5745A5}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83E2AA11-741A-4372-AF00-AE5941BF3DF5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3FB240B-0796-45FB-B497-98BF52C92CD5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{139662B8-254F-4C6E-8F47-0BED968900AC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6767F725-CBBE-41B1-81DE-35A81BA1BF4D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F8719C4-2E8B-4202-B0B6-BDD2BA5745A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A00FEF5C-6B23-45C1-8A8B-06763296E71E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3FB240B-0796-45FB-B497-98BF52C92CD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEAC2E62-3378-4F0A-96AE-5A63F68AD2B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6767F725-CBBE-41B1-81DE-35A81BA1BF4D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{804E6E8A-AF12-405C-80F1-73F29444E85A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A00FEF5C-6B23-45C1-8A8B-06763296E71E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{345E058C-F5EF-475F-8C1C-6603639EEFED}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CEAC2E62-3378-4F0A-96AE-5A63F68AD2B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94B14968-E0D5-4B6C-B289-1DE9064C637A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{804E6E8A-AF12-405C-80F1-73F29444E85A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE697776-1A35-4713-A5F3-AF8184511ED2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{345E058C-F5EF-475F-8C1C-6603639EEFED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{418B1032-6E0F-484D-B3C6-80D18E00627B}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94B14968-E0D5-4B6C-B289-1DE9064C637A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68595C8D-4021-43FD-800D-0B5753F825C7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE697776-1A35-4713-A5F3-AF8184511ED2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA4743E8-593A-4D71-BE91-6C3A04527122}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{418B1032-6E0F-484D-B3C6-80D18E00627B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC1AEBD1-A7AF-4DB5-96DD-3323354C43E9}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68595C8D-4021-43FD-800D-0B5753F825C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B217CFB-F6C6-454D-82E9-D08C00FF8BA4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA4743E8-593A-4D71-BE91-6C3A04527122}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D925EEC6-08A9-4FDD-81AF-C0D98849DA52}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC1AEBD1-A7AF-4DB5-96DD-3323354C43E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{127A59FC-1AD6-48F0-A94B-35BD71AAF816}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B217CFB-F6C6-454D-82E9-D08C00FF8BA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F605062-2854-4E50-A529-1FE2CA0EC024}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D925EEC6-08A9-4FDD-81AF-C0D98849DA52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{008CDB26-4FB1-4E26-9A85-C8876ED74CE8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{127A59FC-1AD6-48F0-A94B-35BD71AAF816}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F538A903-6F54-4DF5-84BF-5EAAE582DC22}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F605062-2854-4E50-A529-1FE2CA0EC024}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EBD0916-6BAC-4843-9488-58A94817B6B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{008CDB26-4FB1-4E26-9A85-C8876ED74CE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7A1681-98A6-4B9F-AFE2-9C370BB4A451}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F538A903-6F54-4DF5-84BF-5EAAE582DC22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72606681-A56C-42E1-93A4-6BB442984F7F}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EBD0916-6BAC-4843-9488-58A94817B6B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14E3B784-8E28-4982-8590-851A7155E41D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E7A1681-98A6-4B9F-AFE2-9C370BB4A451}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5252F045-1418-4CF5-A002-FB864B661782}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72606681-A56C-42E1-93A4-6BB442984F7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43D5709B-EEDE-48F1-8370-45A50C4490F7}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14E3B784-8E28-4982-8590-851A7155E41D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1EEA4BF-5DDF-4E60-AFCE-78A18751594F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5252F045-1418-4CF5-A002-FB864B661782}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA36D897-7423-43FD-973B-7BE37F82129F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43D5709B-EEDE-48F1-8370-45A50C4490F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D651CC06-D911-4153-B32F-C10BBD225C66}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1EEA4BF-5DDF-4E60-AFCE-78A18751594F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34A8F72A-CE21-4615-9CF0-128370F78E7E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA36D897-7423-43FD-973B-7BE37F82129F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66434949-208B-4167-B7F0-0126F7A01412}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D651CC06-D911-4153-B32F-C10BBD225C66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B90460-1FC5-474F-9F5B-43895720F89D}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34A8F72A-CE21-4615-9CF0-128370F78E7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74460922-E3A8-4A7D-A1F5-F62C1E2D6048}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66434949-208B-4167-B7F0-0126F7A01412}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{869492C3-EAC8-41EA-97D7-25634A1BF459}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9B90460-1FC5-474F-9F5B-43895720F89D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B60F08D-8837-41DF-8712-D96B9ABC997C}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74460922-E3A8-4A7D-A1F5-F62C1E2D6048}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D5C6A9B-1B5E-4072-A404-C510F02B4D89}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{869492C3-EAC8-41EA-97D7-25634A1BF459}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFCA788C-A46D-4DF6-9103-E12ED1F95BFB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B60F08D-8837-41DF-8712-D96B9ABC997C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AE5E1E8-E655-4C13-A20A-FC8177DF91CB}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D5C6A9B-1B5E-4072-A404-C510F02B4D89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B1786FA-C76D-4E31-8560-E8738D2CC574}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFCA788C-A46D-4DF6-9103-E12ED1F95BFB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{544BE7A4-4528-46CC-B9D9-D6E46F28B84F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AE5E1E8-E655-4C13-A20A-FC8177DF91CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AEE37DC-C7BE-4165-97DD-79C1804DF5F6}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B1786FA-C76D-4E31-8560-E8738D2CC574}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{129F7F15-47AF-4279-9182-891986F1932B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{544BE7A4-4528-46CC-B9D9-D6E46F28B84F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17691398-7254-48CD-81A7-1A8F95DD67EC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AEE37DC-C7BE-4165-97DD-79C1804DF5F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8ED66DB6-9572-4B62-BF51-0E4BD6A90341}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{129F7F15-47AF-4279-9182-891986F1932B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D238F6DD-03D9-444F-965A-BC14D5A48230}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17691398-7254-48CD-81A7-1A8F95DD67EC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECF84217-4129-4B6F-B1F1-59FF605D5F5C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8ED66DB6-9572-4B62-BF51-0E4BD6A90341}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28166E60-BB1D-4117-83D3-3A29EAD555C9}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D238F6DD-03D9-444F-965A-BC14D5A48230}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8C64A7B-6F0A-447C-8C09-306890146464}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECF84217-4129-4B6F-B1F1-59FF605D5F5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDE87358-EE80-40A3-A0D9-DCF7E27F2D71}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28166E60-BB1D-4117-83D3-3A29EAD555C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7B868AC-C115-416F-81E8-ED1D49C34E5F}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
+++ b/____EvoM1_TraitTable/dexterity_iwaniuk.xlsx
@@ -962,13 +962,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8C64A7B-6F0A-447C-8C09-306890146464}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89B1A2AF-3764-46E6-8378-6806242D1392}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDE87358-EE80-40A3-A0D9-DCF7E27F2D71}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FC98272-AE4E-4810-A28C-8E82727BE6A3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7B868AC-C115-416F-81E8-ED1D49C34E5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7301FE2A-16E9-4BE8-9040-F883DFD39721}"/>
 </file>